--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92567234652</v>
+        <v>46157.93096509336</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93096509336</v>
+        <v>46157.93171598962</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93171598962</v>
+        <v>46157.93399071303</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93399071303</v>
+        <v>46157.93716908283</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716908283</v>
+        <v>46158.28215423035</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28215423035</v>
+        <v>46158.29678730459</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29678730459</v>
+        <v>46158.29813594586</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29813594586</v>
+        <v>46158.33386378347</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33386378347</v>
+        <v>46158.3685615295</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685615295</v>
+        <v>46158.37286875502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
